--- a/북원_시설안내.xlsx
+++ b/북원_시설안내.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\홈페이지 리뉴얼\Claude outputs\시설안내_배포\facility-guide-pack\facility-pack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B2371C-1DDB-4D99-BD5D-9F3FA1DA808E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61760B0D-8493-4EA7-B76F-BB357D27B92F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="146">
   <si>
     <t>시설안내 데이터 — 4행이 헤더, 5행부터 데이터 입력</t>
   </si>
@@ -64,6 +64,9 @@
     <t>건물 전경</t>
   </si>
   <si>
+    <t>9_1.jpg, 9_2.jpg</t>
+  </si>
+  <si>
     <t>f1</t>
   </si>
   <si>
@@ -73,27 +76,66 @@
     <t>사무실</t>
   </si>
   <si>
+    <t>복지관 행정 업무 및 이용자 접수·상담 창구</t>
+  </si>
+  <si>
+    <t>평일 09:00~18:00 방문</t>
+  </si>
+  <si>
     <t>물리치료실</t>
   </si>
   <si>
-    <t>1,2층 키오스크를 통해 예약</t>
-  </si>
-  <si>
-    <t>섬김이 공간</t>
-  </si>
-  <si>
-    <t>이용자의 건강 상태 확인 및 관리</t>
+    <t>1_2.jpg</t>
+  </si>
+  <si>
+    <t>1_2</t>
+  </si>
+  <si>
+    <t>건강관리실</t>
+  </si>
+  <si>
+    <t>1_4_1.jpg, 1_4_2.jpg, 1_4_3.jpg</t>
+  </si>
+  <si>
+    <t>1_4</t>
   </si>
   <si>
     <t>음악실</t>
   </si>
   <si>
+    <t>1_5.jpg</t>
+  </si>
+  <si>
+    <t>수업 등록 후 이용</t>
+  </si>
+  <si>
+    <t>1_5</t>
+  </si>
+  <si>
     <t>상담실</t>
   </si>
   <si>
+    <t>1_6.jpg</t>
+  </si>
+  <si>
+    <t>복지관 상담 요청 시</t>
+  </si>
+  <si>
+    <t>1_6</t>
+  </si>
+  <si>
     <t>회의실</t>
   </si>
   <si>
+    <t>1_7.jpg</t>
+  </si>
+  <si>
+    <t>복지관 업무 회의 및 내빈 방문 시 활용</t>
+  </si>
+  <si>
+    <t>1_7</t>
+  </si>
+  <si>
     <t>f2</t>
   </si>
   <si>
@@ -103,24 +145,90 @@
     <t>온기식당</t>
   </si>
   <si>
+    <t>2_1.jpg</t>
+  </si>
+  <si>
+    <t>어르신 중식 제공 및 경로식당 운영</t>
+  </si>
+  <si>
+    <t>2_1</t>
+  </si>
+  <si>
     <t>요리교실</t>
   </si>
   <si>
+    <t>2_2.jpg</t>
+  </si>
+  <si>
+    <t>2_2</t>
+  </si>
+  <si>
     <t>서예실</t>
   </si>
   <si>
+    <t>2_3.jpg</t>
+  </si>
+  <si>
+    <t>서예·한문·캘리그래피 프로그램 운영</t>
+  </si>
+  <si>
+    <t>2_3</t>
+  </si>
+  <si>
     <t>장기바둑실</t>
   </si>
   <si>
+    <t>2_4.jpg</t>
+  </si>
+  <si>
+    <t>장기·바둑 등 두뇌활동 여가 공간</t>
+  </si>
+  <si>
+    <t>2_4</t>
+  </si>
+  <si>
     <t>정보화실</t>
   </si>
   <si>
+    <t>2_5.jpg</t>
+  </si>
+  <si>
+    <t>컴퓨터·스마트폰 교육 프로그램 운영</t>
+  </si>
+  <si>
+    <t>2_5</t>
+  </si>
+  <si>
     <t>강사대기실</t>
   </si>
   <si>
+    <t>2_6.jpg</t>
+  </si>
+  <si>
+    <t>외부 강사 대기 및 준비 공간</t>
+  </si>
+  <si>
+    <t>강사 전용</t>
+  </si>
+  <si>
+    <t>2_6</t>
+  </si>
+  <si>
     <t>주차장</t>
   </si>
   <si>
+    <t>2_7.jpg</t>
+  </si>
+  <si>
+    <t>복지관 이용자 및 방문자 주차 공간</t>
+  </si>
+  <si>
+    <t>2층 연결 주차장 이용</t>
+  </si>
+  <si>
+    <t>2_7</t>
+  </si>
+  <si>
     <t>f3</t>
   </si>
   <si>
@@ -130,21 +238,69 @@
     <t>다목적체육실</t>
   </si>
   <si>
+    <t>3_1.jpg</t>
+  </si>
+  <si>
+    <t>3_1</t>
+  </si>
+  <si>
     <t>소강당</t>
   </si>
   <si>
+    <t>3_2.jpg</t>
+  </si>
+  <si>
+    <t>프로그램 일정에 따라 운영</t>
+  </si>
+  <si>
+    <t>3_2</t>
+  </si>
+  <si>
     <t>당구실</t>
   </si>
   <si>
+    <t>3_3.jpg</t>
+  </si>
+  <si>
+    <t>당구(캐롬·포켓) 여가 활동 공간</t>
+  </si>
+  <si>
+    <t>3_3</t>
+  </si>
+  <si>
     <t>포켓볼실</t>
   </si>
   <si>
+    <t>3_4.jpg</t>
+  </si>
+  <si>
+    <t>포켓볼 여가 활동 공간</t>
+  </si>
+  <si>
+    <t>3_4</t>
+  </si>
+  <si>
     <t>프로그램실1</t>
   </si>
   <si>
+    <t>3_5.jpg</t>
+  </si>
+  <si>
+    <t>3_5</t>
+  </si>
+  <si>
     <t>야외테라스</t>
   </si>
   <si>
+    <t>3_6.jpg</t>
+  </si>
+  <si>
+    <t>자유 이용</t>
+  </si>
+  <si>
+    <t>3_6</t>
+  </si>
+  <si>
     <t>f4</t>
   </si>
   <si>
@@ -154,253 +310,175 @@
     <t>대강당</t>
   </si>
   <si>
+    <t>4_1_1.jpg, 4_1_2.jpg</t>
+  </si>
+  <si>
+    <t>대규모 행사·공연·강연 개최 공간</t>
+  </si>
+  <si>
+    <t>행사 일정에 따라 운영</t>
+  </si>
+  <si>
+    <t>4_1</t>
+  </si>
+  <si>
+    <t>우리방송국</t>
+  </si>
+  <si>
+    <t>4_2_1.jpg, 4_2_2.jpg</t>
+  </si>
+  <si>
+    <t>복지관 자체 방송 제작 및 미디어 교육 공간</t>
+  </si>
+  <si>
+    <t>4_2</t>
+  </si>
+  <si>
+    <t>우리배움터</t>
+  </si>
+  <si>
+    <t>4_3.jpg</t>
+  </si>
+  <si>
+    <t>소규모 교육 및 학습 프로그램 운영 공간</t>
+  </si>
+  <si>
+    <t>4_3</t>
+  </si>
+  <si>
+    <t>우리소리쉼</t>
+  </si>
+  <si>
+    <t>4_4.jpg</t>
+  </si>
+  <si>
+    <t>4_4</t>
+  </si>
+  <si>
+    <t>우리책이음</t>
+  </si>
+  <si>
+    <t>4_5</t>
+  </si>
+  <si>
+    <t>어르신 독서 및 소규모 도서 열람 공간</t>
+  </si>
+  <si>
+    <t>우리체험터</t>
+  </si>
+  <si>
+    <t>4_6</t>
+  </si>
+  <si>
+    <t>우리키오스크</t>
+  </si>
+  <si>
+    <t>4_7</t>
+  </si>
+  <si>
+    <t>우리갤러리</t>
+  </si>
+  <si>
+    <t>4_8</t>
+  </si>
+  <si>
+    <t>어르신 작품 전시 및 문화 향유 공간</t>
+  </si>
+  <si>
+    <t>자유 관람</t>
+  </si>
+  <si>
+    <t>장독뜰</t>
+  </si>
+  <si>
+    <t>4_9</t>
+  </si>
+  <si>
+    <t>원주시 북부권역의 복지거점, 북원노인종합복지관 입니다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>이용자의 건강증진을 목적으로 물리치료 및 재활 프로그램 운영</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1_1.jpg</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>1_1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>1층</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>이용자의 건강증진을 목적으로 물리치료 및 재활 프로그램 운영</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>수업 등록 후 이용</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>복지관 상담 요청 시</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>복지관 업무 회의 및 내빈 방문 시 활용</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>우리배움터</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>우리방송국</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>우리소리쉼</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>우리책이음</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>우리체험터</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>우리키오스크</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>우리갤러리</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>장독뜰</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2_1.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2_2.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2_3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2_3.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2_4.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2_4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2_5.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2_5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2_6.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>3_6.jpg</t>
-  </si>
-  <si>
-    <t>2_6</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2_7</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>4_7</t>
-  </si>
-  <si>
-    <t>2_7.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>3_1.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>3_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>3_2.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>3_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>3_3.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>3_4</t>
-  </si>
-  <si>
-    <t>3_4.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>3_3</t>
-  </si>
-  <si>
-    <t>3_5.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>3_5</t>
-  </si>
-  <si>
-    <t>3_6</t>
-  </si>
-  <si>
-    <t>4_1_1.jpg, 4_1_2.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>4_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>4_3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>4_4</t>
-  </si>
-  <si>
-    <t>4_5</t>
-  </si>
-  <si>
-    <t>4_6</t>
-  </si>
-  <si>
-    <t>4_8</t>
-  </si>
-  <si>
-    <t>4_9</t>
-  </si>
-  <si>
-    <t>4_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>4_2_1.jpg, 4_2_2.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>4_3.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>4_4.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1_2</t>
-  </si>
-  <si>
-    <t>1_3</t>
-  </si>
-  <si>
-    <t>1_4</t>
-  </si>
-  <si>
-    <t>1_5</t>
-  </si>
-  <si>
-    <t>1_6</t>
-  </si>
-  <si>
-    <t>1_7</t>
-  </si>
-  <si>
-    <t>1_1.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1_2.jpg</t>
-  </si>
-  <si>
-    <t>1_3.jpg</t>
-  </si>
-  <si>
-    <t>1_5.jpg</t>
-  </si>
-  <si>
-    <t>1_6.jpg</t>
-  </si>
-  <si>
-    <t>1_7.jpg</t>
-  </si>
-  <si>
-    <t>9_1.jpg, 9_2.jpg</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>건강관리실</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1_4_1.jpg, 1_4_2.jpg, 1_4_3.jpg</t>
+    <t>체력증진을 위한 운동기기 및 프로그램 운영</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>음악(악기) 관련 프로그램 운영</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>개별 상담 및 사례관리 면담 진행</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>복지관 이용 등록 후 키오스크 발권</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>요리 실습, 봉사단 제과/제빵 프로그램 운영</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>이용 등록 후 자율 이용</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>탁구실 운영</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1~4층 키오스크를 통해 예약</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>댄스, 요가, 필라테스 등 50명 이내 프로그램 운영</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>언어, 공예 등 소규모 인원 프로그램 운영</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>야외 휴식 공간</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>자유 이용</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>신체적, 정신적 여유로운 쉼을 위한 공간</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 기기 활용에 최적화된 체험 공간</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>일상생활에서 접하는 여러 키오스크 체험</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>복지관 전경이 보이는 편안한 쉼터</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>4_5_1.jpg, 4_5_2.jpg</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -515,16 +593,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -829,28 +908,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6" style="6" customWidth="1"/>
+    <col min="2" max="2" width="10" style="6" customWidth="1"/>
+    <col min="3" max="3" width="8" style="6" customWidth="1"/>
+    <col min="4" max="4" width="14" style="6" customWidth="1"/>
+    <col min="5" max="5" width="20" style="6" customWidth="1"/>
+    <col min="6" max="6" width="67" style="6" customWidth="1"/>
+    <col min="7" max="7" width="30" style="6" customWidth="1"/>
+    <col min="8" max="8" width="9.875" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:8" ht="17.25" customHeight="1">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
@@ -899,11 +979,13 @@
         <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="G5" s="3"/>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>9</v>
       </c>
     </row>
@@ -912,21 +994,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="5" t="s">
-        <v>44</v>
+        <v>126</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -934,25 +1020,25 @@
         <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>97</v>
+        <v>136</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -960,21 +1046,25 @@
         <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="5" t="s">
-        <v>98</v>
+        <v>24</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -982,23 +1072,25 @@
         <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="5" t="s">
-        <v>99</v>
+        <v>129</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1006,23 +1098,25 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F10" s="3"/>
+        <v>31</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="G10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>100</v>
+        <v>32</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1030,23 +1124,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="G11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>101</v>
+        <v>131</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1054,23 +1150,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="5" t="s">
-        <v>102</v>
+        <v>42</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1078,21 +1176,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="H13" s="4" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1100,21 +1202,25 @@
         <v>10</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="5" t="s">
-        <v>60</v>
+        <v>48</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1122,21 +1228,25 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="5" t="s">
-        <v>62</v>
+        <v>52</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1144,21 +1254,25 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+        <v>56</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="H16" s="5" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1166,21 +1280,25 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="6" t="s">
-        <v>67</v>
+        <v>60</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1188,21 +1306,25 @@
         <v>10</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="6" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1210,21 +1332,25 @@
         <v>10</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="6" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1232,21 +1358,25 @@
         <v>10</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="6" t="s">
         <v>75</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1254,21 +1384,25 @@
         <v>10</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1276,21 +1410,25 @@
         <v>10</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1298,21 +1436,25 @@
         <v>10</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="6" t="s">
-        <v>79</v>
+        <v>87</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1320,21 +1462,25 @@
         <v>10</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="6" t="s">
-        <v>83</v>
+        <v>90</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1342,21 +1488,25 @@
         <v>10</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1364,21 +1514,25 @@
         <v>10</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="6" t="s">
-        <v>93</v>
+        <v>101</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1386,21 +1540,25 @@
         <v>10</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="H27" s="3" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1408,21 +1566,25 @@
         <v>10</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
+        <v>109</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="H28" s="3" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1430,21 +1592,25 @@
         <v>10</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+        <v>145</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="H29" s="3" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1452,21 +1618,25 @@
         <v>10</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+        <v>115</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="H30" s="3" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1474,21 +1644,25 @@
         <v>10</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+        <v>117</v>
+      </c>
+      <c r="F31" t="s">
+        <v>143</v>
+      </c>
+      <c r="G31" t="s">
+        <v>91</v>
+      </c>
       <c r="H31" s="3" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1496,19 +1670,25 @@
         <v>10</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>72</v>
+        <v>119</v>
+      </c>
+      <c r="F32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G32" t="s">
+        <v>121</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>72</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1516,39 +1696,25 @@
         <v>10</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>91</v>
+        <v>123</v>
+      </c>
+      <c r="F33" t="s">
+        <v>144</v>
+      </c>
+      <c r="G33" t="s">
+        <v>131</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/북원_시설안내.xlsx
+++ b/북원_시설안내.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\홈페이지 리뉴얼\Claude outputs\시설안내_배포\facility-guide-pack\facility-pack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61760B0D-8493-4EA7-B76F-BB357D27B92F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA48C534-B5E2-4070-A61C-C06613B81D4B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10995" yWindow="0" windowWidth="17040" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시설안내" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="140">
   <si>
     <t>시설안내 데이터 — 4행이 헤더, 5행부터 데이터 입력</t>
   </si>
@@ -34,9 +34,6 @@
     <t>게시</t>
   </si>
   <si>
-    <t>층코드</t>
-  </si>
-  <si>
     <t>층명</t>
   </si>
   <si>
@@ -55,9 +52,6 @@
     <t>O</t>
   </si>
   <si>
-    <t>exterior</t>
-  </si>
-  <si>
     <t>전경</t>
   </si>
   <si>
@@ -67,9 +61,6 @@
     <t>9_1.jpg, 9_2.jpg</t>
   </si>
   <si>
-    <t>f1</t>
-  </si>
-  <si>
     <t>1층</t>
   </si>
   <si>
@@ -136,9 +127,6 @@
     <t>1_7</t>
   </si>
   <si>
-    <t>f2</t>
-  </si>
-  <si>
     <t>2층</t>
   </si>
   <si>
@@ -229,9 +217,6 @@
     <t>2_7</t>
   </si>
   <si>
-    <t>f3</t>
-  </si>
-  <si>
     <t>3층</t>
   </si>
   <si>
@@ -299,9 +284,6 @@
   </si>
   <si>
     <t>3_6</t>
-  </si>
-  <si>
-    <t>f4</t>
   </si>
   <si>
     <t>4층</t>
@@ -908,20 +890,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6" style="6" customWidth="1"/>
-    <col min="2" max="2" width="10" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8" style="6" customWidth="1"/>
-    <col min="4" max="4" width="14" style="6" customWidth="1"/>
-    <col min="5" max="5" width="20" style="6" customWidth="1"/>
-    <col min="6" max="6" width="67" style="6" customWidth="1"/>
-    <col min="7" max="7" width="30" style="6" customWidth="1"/>
-    <col min="8" max="8" width="9.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="6" customWidth="1"/>
+    <col min="3" max="3" width="14" style="6" customWidth="1"/>
+    <col min="4" max="4" width="20" style="6" customWidth="1"/>
+    <col min="5" max="5" width="67" style="6" customWidth="1"/>
+    <col min="6" max="6" width="30" style="6" customWidth="1"/>
+    <col min="7" max="7" width="9.875" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.25" customHeight="1">
+    <row r="1" spans="1:7" ht="17.25" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -930,19 +911,18 @@
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
       <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -961,765 +941,675 @@
       <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="G6" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="3" t="s">
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="G24" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H23" s="5" t="s">
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H24" s="5" t="s">
+      <c r="E25" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="G25" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>94</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F26" s="3" t="s">
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="H26" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="3" t="s">
+      <c r="E28" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E27" s="3" t="s">
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="D29" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" s="3" t="s">
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H28" s="3" t="s">
+      <c r="E30" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="E31" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="3" t="s">
+      <c r="E32" t="s">
         <v>114</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="F32" t="s">
         <v>115</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D31" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F31" t="s">
-        <v>143</v>
-      </c>
-      <c r="G31" t="s">
-        <v>91</v>
-      </c>
-      <c r="H31" s="3" t="s">
+      <c r="E33" t="s">
+        <v>138</v>
+      </c>
+      <c r="F33" t="s">
+        <v>125</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F32" t="s">
-        <v>120</v>
-      </c>
-      <c r="G32" t="s">
-        <v>121</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F33" t="s">
-        <v>144</v>
-      </c>
-      <c r="G33" t="s">
-        <v>131</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/북원_시설안내.xlsx
+++ b/북원_시설안내.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시설안내" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기관정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -89,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,6 +109,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -473,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -532,6 +534,13 @@
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>■ 게시 : O=보임 / X=숨김</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ '기관정보' 시트: 시설안내 맨 위 기관명·주소·전화 등. 항목/내용 한 줄씩.</t>
         </is>
       </c>
     </row>
@@ -1530,4 +1539,136 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>기관 정보  —  시설안내 맨 위에 나오는 내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>한 줄 = 한 항목. 순서대로 나옵니다. 필요 없으면 줄을 비우세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>기관명</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>북원노인종합복지관</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>운영법인</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>사회복지법인 밥상공동체복지재단</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>설치신고</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>2023. 5. 23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>소재지</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>강원도 원주시 흥양로50번길 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>전화번호</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>033-747-0516</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>팩스</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>033-747-0517</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>시설규모</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>지하 1층, 지상 4층, 연면적 2,879㎡</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>